--- a/results/run_annee_dyn/metrics_rc.xlsx
+++ b/results/run_annee_dyn/metrics_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,6 +580,186 @@
         <v>0.0004195000001345761</v>
       </c>
       <c r="M3" t="inlineStr">
+        <is>
+          <t>RC pas de temps 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>89.38332677196068</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9.454275581553601</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8.76591370570172</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19.6340359502612</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-8.757767480782059</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-7.92945329708523</v>
+      </c>
+      <c r="H4" t="n">
+        <v>42.95570292826048</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12.68483552451694</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.561577673520113</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0003507235224750724</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2392415999984223</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RC pas de temps</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>157.6011883386188</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.55393119061192</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.15038952547717</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25.90015358159213</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-11.06688704457055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-23.76973634948163</v>
+      </c>
+      <c r="H5" t="n">
+        <v>57.88539384990364</v>
+      </c>
+      <c r="I5" t="n">
+        <v>35.1251994813352</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.926651624765471</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.00790802935529868</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.00190650000149617</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>RC pas de temps 24h</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>89.38332677196068</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9.454275581553601</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8.76591370570172</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.6340359502612</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-8.757767480782059</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-7.92945329708523</v>
+      </c>
+      <c r="H6" t="n">
+        <v>42.95570292826048</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12.68483552451694</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.561577673520113</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0003507235224750724</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.204494399997202</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>RC pas de temps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>157.6011883386188</v>
+      </c>
+      <c r="C7" t="n">
+        <v>12.55393119061192</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11.15038952547717</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25.90015358159213</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-11.06688704457055</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-23.76973634948163</v>
+      </c>
+      <c r="H7" t="n">
+        <v>57.88539384990364</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.1251994813352</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.926651624765471</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.00790802935529868</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.003152600002067629</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>RC pas de temps 24h</t>
         </is>
